--- a/outputs/EnergyBae_Solar_Report.xlsx
+++ b/outputs/EnergyBae_Solar_Report.xlsx
@@ -643,7 +643,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>RANJANA MADHUSHAM KHOBRAGADE</t>
+          <t>SHRI MADHUSHAM ROOPCHAND KHOBRAGADE</t>
         </is>
       </c>
       <c r="E1" s="10" t="n"/>
@@ -684,7 +684,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>439322232375</t>
+          <t>439320095567</t>
         </is>
       </c>
       <c r="E2" s="9" t="n"/>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>137.6</v>
+        <v>58.4</v>
       </c>
       <c r="E3" s="17" t="n"/>
       <c r="F3" s="10" t="n"/>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="D4" s="12" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="E4" s="9" t="n"/>
       <c r="F4" s="10" t="n"/>
@@ -979,7 +979,7 @@
         <v>45689</v>
       </c>
       <c r="D9" s="26" t="n">
-        <v>137</v>
+        <v>25</v>
       </c>
       <c r="E9" s="27" t="n"/>
       <c r="F9" s="37" t="n"/>
@@ -1020,7 +1020,7 @@
         <v>45717</v>
       </c>
       <c r="D10" s="26" t="n">
-        <v>35</v>
+        <v>121</v>
       </c>
       <c r="E10" s="27" t="n"/>
       <c r="F10" s="37" t="n"/>
@@ -1061,7 +1061,7 @@
         <v>45748</v>
       </c>
       <c r="D11" s="26" t="n">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E11" s="27" t="n"/>
       <c r="F11" s="37" t="n"/>
@@ -1102,7 +1102,7 @@
         <v>45778</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="E12" s="27" t="n"/>
       <c r="F12" s="37" t="n"/>
@@ -1143,7 +1143,7 @@
         <v>45809</v>
       </c>
       <c r="D13" s="26" t="n">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="E13" s="27" t="n"/>
       <c r="F13" s="37" t="n"/>
@@ -1184,7 +1184,7 @@
         <v>45839</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>229</v>
+        <v>86</v>
       </c>
       <c r="E14" s="32" t="n"/>
       <c r="F14" s="37" t="n"/>
@@ -1225,7 +1225,7 @@
         <v>45870</v>
       </c>
       <c r="D15" s="26" t="n">
-        <v>371</v>
+        <v>96</v>
       </c>
       <c r="E15" s="32" t="n"/>
       <c r="F15" s="37" t="n"/>
@@ -1266,7 +1266,7 @@
         <v>45901</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>364</v>
+        <v>262</v>
       </c>
       <c r="E16" s="32" t="n"/>
       <c r="F16" s="37" t="n"/>
@@ -1307,7 +1307,7 @@
         <v>45931</v>
       </c>
       <c r="D17" s="26" t="n">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="E17" s="32" t="n"/>
       <c r="F17" s="37" t="n"/>
@@ -1348,7 +1348,7 @@
         <v>45962</v>
       </c>
       <c r="D18" s="26" t="n">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="E18" s="32" t="n"/>
       <c r="F18" s="37" t="n"/>
@@ -1389,7 +1389,7 @@
         <v>45992</v>
       </c>
       <c r="D19" s="26" t="n">
-        <v>27</v>
+        <v>151</v>
       </c>
       <c r="E19" s="32" t="n"/>
       <c r="F19" s="37" t="n"/>
@@ -1430,10 +1430,10 @@
         <v>46023</v>
       </c>
       <c r="D20" s="26" t="n">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="E20" s="32" t="n">
-        <v>3440</v>
+        <v>1460</v>
       </c>
       <c r="F20" s="37">
         <f>(E20-$D$3)/D20</f>

--- a/outputs/EnergyBae_Solar_Report.xlsx
+++ b/outputs/EnergyBae_Solar_Report.xlsx
@@ -643,7 +643,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>SHRI MADHUSHAM ROOPCHAND KHOBRAGADE</t>
+          <t>RANJANA MADHUSHAM KHOBRAGADE</t>
         </is>
       </c>
       <c r="E1" s="10" t="n"/>
@@ -684,7 +684,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>439320095567</t>
+          <t>439322232375</t>
         </is>
       </c>
       <c r="E2" s="9" t="n"/>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>58.4</v>
+        <v>137.6</v>
       </c>
       <c r="E3" s="17" t="n"/>
       <c r="F3" s="10" t="n"/>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="D4" s="12" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="E4" s="9" t="n"/>
       <c r="F4" s="10" t="n"/>
@@ -979,7 +979,7 @@
         <v>45689</v>
       </c>
       <c r="D9" s="26" t="n">
-        <v>25</v>
+        <v>137</v>
       </c>
       <c r="E9" s="27" t="n"/>
       <c r="F9" s="37" t="n"/>
@@ -1020,7 +1020,7 @@
         <v>45717</v>
       </c>
       <c r="D10" s="26" t="n">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="E10" s="27" t="n"/>
       <c r="F10" s="37" t="n"/>
@@ -1061,7 +1061,7 @@
         <v>45748</v>
       </c>
       <c r="D11" s="26" t="n">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E11" s="27" t="n"/>
       <c r="F11" s="37" t="n"/>
@@ -1102,7 +1102,7 @@
         <v>45778</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="E12" s="27" t="n"/>
       <c r="F12" s="37" t="n"/>
@@ -1143,7 +1143,7 @@
         <v>45809</v>
       </c>
       <c r="D13" s="26" t="n">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="E13" s="27" t="n"/>
       <c r="F13" s="37" t="n"/>
@@ -1184,7 +1184,7 @@
         <v>45839</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>86</v>
+        <v>229</v>
       </c>
       <c r="E14" s="32" t="n"/>
       <c r="F14" s="37" t="n"/>
@@ -1225,7 +1225,7 @@
         <v>45870</v>
       </c>
       <c r="D15" s="26" t="n">
-        <v>96</v>
+        <v>371</v>
       </c>
       <c r="E15" s="32" t="n"/>
       <c r="F15" s="37" t="n"/>
@@ -1266,7 +1266,7 @@
         <v>45901</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>262</v>
+        <v>364</v>
       </c>
       <c r="E16" s="32" t="n"/>
       <c r="F16" s="37" t="n"/>
@@ -1307,7 +1307,7 @@
         <v>45931</v>
       </c>
       <c r="D17" s="26" t="n">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="E17" s="32" t="n"/>
       <c r="F17" s="37" t="n"/>
@@ -1348,7 +1348,7 @@
         <v>45962</v>
       </c>
       <c r="D18" s="26" t="n">
-        <v>258</v>
+        <v>152</v>
       </c>
       <c r="E18" s="32" t="n"/>
       <c r="F18" s="37" t="n"/>
@@ -1389,7 +1389,7 @@
         <v>45992</v>
       </c>
       <c r="D19" s="26" t="n">
-        <v>151</v>
+        <v>27</v>
       </c>
       <c r="E19" s="32" t="n"/>
       <c r="F19" s="37" t="n"/>
@@ -1430,10 +1430,10 @@
         <v>46023</v>
       </c>
       <c r="D20" s="26" t="n">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="E20" s="32" t="n">
-        <v>1460</v>
+        <v>3440</v>
       </c>
       <c r="F20" s="37">
         <f>(E20-$D$3)/D20</f>
